--- a/testdata/EmployeeAdjustmentData.xlsx
+++ b/testdata/EmployeeAdjustmentData.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -681,15 +681,18 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="180" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -698,7 +701,7 @@
     <cellStyle name="Percent" xfId="3" builtinId="5"/>
     <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
     <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
     <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
     <cellStyle name="Note" xfId="8" builtinId="10"/>
     <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
@@ -1226,7 +1229,7 @@
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="2" max="2" width="8.90909090909091"/>
+    <col min="2" max="2" width="9.63636363636364"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1251,15 +1254,15 @@
         <v>5</v>
       </c>
       <c r="B2" s="3">
-        <v>45800</v>
+        <v>45946</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="2">
-        <v>4000</v>
+      <c r="D2" s="4">
+        <v>5000</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="4">
         <v>1</v>
       </c>
     </row>

--- a/testdata/EmployeeAdjustmentData.xlsx
+++ b/testdata/EmployeeAdjustmentData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="6920"/>
+    <workbookView windowWidth="13860" windowHeight="6920"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
